--- a/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est au parc avec papa. Sa sœur Ava est sur la balançoire. La balançoire va et vient. Noé la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Noé dit : je suis jaloux. Papa écoute. Noé va près d'Ava. Il dit : je voudrais demander un tour. Ava dit : encore un peu. Noé attend la réponse. Il compte les allers. Il reste les mains sur ses genoux. Puis Ava descend. Noé a son tour. Il se balance doucement. Papa dit : tu as demandé un tour. Tu as attendu la réponse.</t>
+          <t>Noé est au parc avec papa. Sa sœur Ava est sur la balançoire. La balançoire va et vient. Noé la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Je suis jaloux. Papa écoute. Noé va près d'Ava. Je voudrais demander un tour. Encore un peu. Noé attend la réponse. Il compte les allers. Il reste les mains sur ses genoux. Puis Ava descend. Noé a son tour. Il se balance doucement. Tu as demandé un tour. Tu as attendu la réponse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est au parc avec papa. Sa sœur Ava est sur la balançoire. La balançoire va et vient. Noé la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire.
+enfant-m|Je suis jaloux. Papa écoute.
+narrateur|Noé va près d'Ava.
+narrateur|Je voudrais demander un tour.
+copine|Encore un peu.
+narrateur|Noé attend la réponse. Il compte les allers. Il reste les mains sur ses genoux. Puis Ava descend. Noé a son tour. Il se balance doucement.
+papa|Tu as demandé un tour. Tu as attendu la réponse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé veut la balançoire. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé descend. Ava reprend un tour. Papa reste au banc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 papa|Tu as demandé un tour. Tu as attendu la réponse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Noé veut la balançoire. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Noé a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Noé descend. Ava reprend un tour. Papa reste au banc.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Demander un tour et attendre la réponse</t>
+          <t>Le tour de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah est sur la balançoire. Victorino a le ventre serré. Il dit qu'il est jaloux. Il demande un tour. Il attend.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé est au parc avec papa. Sa sœur Ava est sur la balançoire. La balançoire va et vient. Noé la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Je suis jaloux. Papa écoute. Noé va près d'Ava. Je voudrais demander un tour. Encore un peu. Noé attend la réponse. Il compte les allers. Il reste les mains sur ses genoux. Puis Ava descend. Noé a son tour. Il se balance doucement. Tu as demandé un tour. Tu as attendu la réponse.</t>
+          <t>Un pigeon gris est sur la barrière. Il picore un tout petit caillou. Le chemin du parc a du gravier. Les cailloux font crac, sous les pieds. Une chaîne de balançoire tinte. Un sac en toile attend sur le banc. L'herbe sent l'après-pluie. Je reste sur le banc, Victorino. Sarah est déjà près de la balançoire. Le pigeon est gris, papa. Oui. Il picore tout doux. On marche sur le gravier. En ce moment, Sarah se balance. La balançoire va et vient. Victorino la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Victorino va près de Sarah. Je voudrais demander un tour. Encore un peu. On attend la réponse. Victorino attend. Il compte les allers. Un. Deux. Trois. Ses mains restent sur ses genoux. Le gravier est froid sous les chaussures. Puis Sarah descend. C'est ton tour. Merci, Sarah. Victorino a son tour. Il se balance doucement. La chaîne tinte encore. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Victorino. Tu as fait du bon travail. J'ai dit : je suis jaloux. Puis tu as demandé. Le pigeon s'envole un peu. Le sac en toile reste sur le banc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé est au parc avec papa. Sa sœur Ava est sur la balançoire. La balançoire va et vient. Noé la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire.
-enfant-m|Je suis jaloux. Papa écoute.
-narrateur|Noé va près d'Ava.
-narrateur|Je voudrais demander un tour.
-copine|Encore un peu.
-narrateur|Noé attend la réponse. Il compte les allers. Il reste les mains sur ses genoux. Puis Ava descend. Noé a son tour. Il se balance doucement.
-papa|Tu as demandé un tour. Tu as attendu la réponse.</t>
+          <t>narrateur|Un pigeon gris est sur la barrière.
+narrateur|Il picore un tout petit caillou.
+narrateur|Le chemin du parc a du gravier.
+narrateur|Les cailloux font crac, sous les pieds.
+narrateur|Une chaîne de balançoire tinte.
+narrateur|Un sac en toile attend sur le banc.
+narrateur|L'herbe sent l'après-pluie.
+maman|Je reste sur le banc, Victorino.
+papa|Sarah est déjà près de la balançoire.
+enfant-m|Le pigeon est gris, papa.
+papa|Oui. Il picore tout doux.
+maman|On marche sur le gravier.
+narrateur|En ce moment, Sarah se balance.
+narrateur|La balançoire va et vient.
+narrateur|Victorino la regarde longtemps.
+narrateur|Son ventre se serre.
+narrateur|Ses yeux restent sur la balançoire.
+narrateur|Ses mains restent sur ses genoux.
+enfant-m|Je suis jaloux.
+papa|Je t'écoute.
+maman|Jaloux, c'est cette envie.
+papa|On peut le dire.
+narrateur|Victorino va près de Sarah.
+enfant-m|Je voudrais demander un tour.
+enfant-f|Encore un peu.
+papa|On attend la réponse.
+narrateur|Victorino attend.
+narrateur|Il compte les allers.
+narrateur|Un. Deux. Trois.
+narrateur|Ses mains restent sur ses genoux.
+narrateur|Le gravier est froid sous les chaussures.
+narrateur|Puis Sarah descend.
+enfant-f|C'est ton tour.
+enfant-m|Merci, Sarah.
+narrateur|Victorino a son tour.
+narrateur|Il se balance doucement.
+narrateur|La chaîne tinte encore.
+papa|Tu as demandé un tour.
+papa|Tu as attendu la réponse.
+maman|Bravo, Victorino.
+maman|Tu as fait du bon travail.
+enfant-m|J'ai dit : je suis jaloux.
+papa|Puis tu as demandé.
+narrateur|Le pigeon s'envole un peu.
+narrateur|Le sac en toile reste sur le banc.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé veut la balançoire. Que fait-il ?</t>
+          <t>Victorino veut la balançoire. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1434,7 +1484,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,7 +1556,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé veut la balançoire. Que fait-il ?</t>
+          <t>narrateur|Victorino veut la balançoire.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1585,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+          <t>Victorino a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Bravo. C'est du bon travail. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La chaîne tinte, tout doux. Le gravier reste gris. Tu as attendu Sarah. Elle a dit : encore un peu. Puis elle a dit : c'est ton tour. Le pigeon est revenu sur la barrière.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1595,14 +1646,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1678,7 +1729,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+          <t>narrateur|Victorino a nommé : jaloux.
+narrateur|Il a demandé un tour.
+narrateur|Il a attendu la réponse.
+enfant-m|J'ai demandé. J'ai attendu.
+papa|Oui. Les mains sur les genoux.
+maman|Bravo. C'est du bon travail.
+enfant-f|Après, c'est encore mon tour ?
+papa|On demande. On attend.
+enfant-m|Oui. On demande un tour.
+maman|Jaloux, on le dit.
+narrateur|La chaîne tinte, tout doux.
+narrateur|Le gravier reste gris.
+papa|Tu as attendu Sarah.
+enfant-m|Elle a dit : encore un peu.
+maman|Puis elle a dit : c'est ton tour.
+narrateur|Le pigeon est revenu sur la barrière.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1772,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé descend. Ava reprend un tour. Papa reste au banc.</t>
+          <t>Victorino descend. Sarah reprend un tour. Je reste près du banc. Le sac est là, avec le goûter. J'ai eu mon tour. Oui. Tu as demandé. La chaîne tinte encore. On écoute, un peu. Victorino s'assoit près de maman. Le bois du banc est un peu froid. Tu as attendu la réponse. Mes mains étaient sur mes genoux. C'est le bon geste. Sarah se balance, tout doux. L'herbe sent encore l'après-pluie.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1767,14 +1833,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1842,10 +1908,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé descend. Ava reprend un tour. Papa reste au banc.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorino descend.
+narrateur|Sarah reprend un tour.
+papa|Je reste près du banc.
+maman|Le sac est là, avec le goûter.
+enfant-m|J'ai eu mon tour.
+papa|Oui. Tu as demandé.
+enfant-f|La chaîne tinte encore.
+maman|On écoute, un peu.
+narrateur|Victorino s'assoit près de maman.
+narrateur|Le bois du banc est un peu froid.
+papa|Tu as attendu la réponse.
+enfant-m|Mes mains étaient sur mes genoux.
+maman|C'est le bon geste.
+narrateur|Sarah se balance, tout doux.
+narrateur|L'herbe sent encore l'après-pluie.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Sarah a eu son tour, aussi. Le pigeon picore encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1938,7 +2022,7 @@
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,7 +2094,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais jaloux. J'ai demandé un tour.
+papa|Tu as attendu. Bravo.
+maman|Sarah a eu son tour, aussi.
+narrateur|Le pigeon picore encore.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un pigeon gris est sur la barrière. Il picore un tout petit caillou. Le chemin du parc a du gravier. Les cailloux font crac, sous les pieds. Une chaîne de balançoire tinte. Un sac en toile attend sur le banc. L'herbe sent l'après-pluie. Je reste sur le banc, Victorino. Sarah est déjà près de la balançoire. Le pigeon est gris, papa. Oui. Il picore tout doux. On marche sur le gravier. En ce moment, Sarah se balance. La balançoire va et vient. Victorino la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Victorino va près de Sarah. Je voudrais demander un tour. Encore un peu. On attend la réponse. Victorino attend. Il compte les allers. Un. Deux. Trois. Ses mains restent sur ses genoux. Le gravier est froid sous les chaussures. Puis Sarah descend. C'est ton tour. Merci, Sarah. Victorino a son tour. Il se balance doucement. La chaîne tinte encore. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Victorino. Tu as fait du bon travail. J'ai dit : je suis jaloux. Puis tu as demandé. Le pigeon s'envole un peu. Le sac en toile reste sur le banc.</t>
+          <t>Un pigeon gris est sur la barrière. Il picore un tout petit caillou. Le chemin du parc a du gravier. Les cailloux font crac, sous les pieds. Une chaîne de balançoire tinte. Un sac en toile attend sur le banc. L'herbe sent l'après-pluie. Je reste sur le banc, Victorino. Sarah est déjà près de la balançoire. Le pigeon est gris, papa. Oui. Il picore tout doux. On marche sur le gravier. En ce moment, Sarah se balance. La balançoire va et vient. Victorino la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Victorino va près de Sarah. Je voudrais demander un tour. Encore un peu. On attend la réponse. Victorino attend. Il compte les allers. Un. Deux. Trois. Ses mains restent sur ses genoux. Le gravier est froid sous les chaussures. Puis Sarah descend. C'est ton tour. Merci, Sarah. Victorino a son tour. Il se balance doucement. La chaîne tinte encore. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Victorino. J'ai dit : je suis jaloux. Puis tu as demandé. Le pigeon s'envole un peu. Le sac en toile reste sur le banc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé est au parc avec papa. Sa sœur Ava est sur la balançoire. La balançoire va et vient. Noé la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Noé dit : je suis &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Papa écoute. Noé va près d'Ava. Il dit : je voudrais demander un tour. Ava dit : encore un peu. Noé attend la réponse. Il compte les allers. Il reste les mains sur ses genoux. Puis Ava descend. Noé a son tour. Il se balance doucement. Papa dit : tu as demandé un tour. Tu as attendu la réponse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un pigeon gris est sur la barrière. Il picore un tout petit caillou. Le chemin du parc a du gravier. Les cailloux font crac, sous les pieds. Une chaîne de balançoire tinte. Un sac en toile attend sur le banc. L'herbe sent l'après-pluie. Je reste sur le banc, Victorino. Sarah est déjà près de la balançoire. Le pigeon est gris, papa. Oui. Il picore tout doux. On marche sur le gravier. En ce moment, Sarah se balance. La balançoire va et vient. Victorino la regarde longtemps. Son ventre se serre. Ses yeux restent sur la balançoire. Ses mains restent sur ses genoux. Je suis jaloux. Je t'écoute. Jaloux, c'est cette envie. On peut le dire. Victorino va près de Sarah. Je voudrais demander un tour. Encore un peu. On attend la réponse. Victorino attend. Il compte les allers. Un. Deux. Trois. Ses mains restent sur ses genoux. Le gravier est froid sous les chaussures. Puis Sarah descend. C'est ton tour. Merci, Sarah. Victorino a son tour. Il se balance doucement. La chaîne tinte encore. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Victorino. J'ai dit : je suis jaloux. Puis tu as demandé. Le pigeon s'envole un peu. Le sac en toile reste sur le banc.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 papa|Tu as demandé un tour.
 papa|Tu as attendu la réponse.
 maman|Bravo, Victorino.
-maman|Tu as fait du bon travail.
 enfant-m|J'ai dit : je suis jaloux.
 papa|Puis tu as demandé.
 narrateur|Le pigeon s'envole un peu.
@@ -1405,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé veut la balançoire. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino veut la balançoire. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1560,7 +1559,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1585,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Bravo. C'est du bon travail. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La chaîne tinte, tout doux. Le gravier reste gris. Tu as attendu Sarah. Elle a dit : encore un peu. Puis elle a dit : c'est ton tour. Le pigeon est revenu sur la barrière.</t>
+          <t>Victorino a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La chaîne tinte, tout doux. Le gravier reste gris. Tu as attendu Sarah. Elle a dit : encore un peu. Puis elle a dit : c'est ton tour. Le pigeon est revenu sur la barrière.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé a nommé : &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Il a demandé un tour. Il a attendu la réponse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La chaîne tinte, tout doux. Le gravier reste gris. Tu as attendu Sarah. Elle a dit : encore un peu. Puis elle a dit : c'est ton tour. Le pigeon est revenu sur la barrière.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1734,7 +1732,6 @@
 narrateur|Il a attendu la réponse.
 enfant-m|J'ai demandé. J'ai attendu.
 papa|Oui. Les mains sur les genoux.
-maman|Bravo. C'est du bon travail.
 enfant-f|Après, c'est encore mon tour ?
 papa|On demande. On attend.
 enfant-m|Oui. On demande un tour.
@@ -1747,7 +1744,6 @@
 narrateur|Le pigeon est revenu sur la barrière.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1777,7 +1773,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé descend. Ava reprend un tour. Papa reste au banc.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino descend. Sarah reprend un tour. Je reste près du banc. Le sac est là, avec le goûter. J'ai eu mon tour. Oui. Tu as demandé. La chaîne tinte encore. On écoute, un peu. Victorino s'assoit près de maman. Le bois du banc est un peu froid. Tu as attendu la réponse. Mes mains étaient sur mes genoux. C'est le bon geste. Sarah se balance, tout doux. L'herbe sent encore l'après-pluie.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1954,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Sarah a eu son tour, aussi. Le pigeon picore encore. L'histoire est finie.</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Sarah a eu son tour, aussi. Le pigeon picore encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais jaloux. J'ai demandé un tour. Tu as attendu. Bravo. Sarah a eu son tour, aussi. Le pigeon picore encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,11 +2093,9 @@
           <t>enfant-m|J'étais jaloux. J'ai demandé un tour.
 papa|Tu as attendu. Bravo.
 maman|Sarah a eu son tour, aussi.
-narrateur|Le pigeon picore encore.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pigeon picore encore.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-01.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, Ava, papa</t>
+          <t>Victorino, Sarah, papa, maman</t>
         </is>
       </c>
     </row>
